--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104759_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104759_W34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0001</v>
+        <v>5.4041</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0376</v>
+        <v>3.6298</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9625</v>
+        <v>1.7743</v>
       </c>
       <c r="G2" t="n">
         <v>2.4285</v>
@@ -610,13 +610,13 @@
         <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5666</v>
+        <v>-0.1626</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8364</v>
+        <v>-0.2442</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2698</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>1.0895</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.312</v>
+        <v>2.8452</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8867</v>
+        <v>4.4826</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5747</v>
+        <v>-1.6374</v>
       </c>
       <c r="G3" t="n">
         <v>2.6048</v>
@@ -688,13 +688,13 @@
         <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1334</v>
+        <v>0.6666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7614</v>
+        <v>0.3573</v>
       </c>
       <c r="U3" t="n">
-        <v>0.372</v>
+        <v>0.3093</v>
       </c>
       <c r="V3" t="n">
         <v>-1.792</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1935</v>
+        <v>2.6743</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8621</v>
+        <v>2.2174</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3314</v>
+        <v>0.4569</v>
       </c>
       <c r="G4" t="n">
         <v>-0.068</v>
@@ -766,13 +766,13 @@
         <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.036</v>
+        <v>-0.5552</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9061</v>
+        <v>-0.5508</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1299</v>
+        <v>-0.0044</v>
       </c>
       <c r="V4" t="n">
         <v>1.4764</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2737</v>
+        <v>1.2909</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5908</v>
+        <v>-0.1658</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8645</v>
+        <v>1.4567</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8843</v>
@@ -844,13 +844,13 @@
         <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2475</v>
+        <v>1.2648</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0926</v>
+        <v>0.5177</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1549</v>
+        <v>0.7471</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3102</v>
+        <v>-0.7071</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5964</v>
+        <v>-0.2328</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2862</v>
+        <v>-0.4744</v>
       </c>
       <c r="G6" t="n">
         <v>-3.3527</v>
@@ -922,13 +922,13 @@
         <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2077</v>
+        <v>0.1903</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0402</v>
+        <v>0.2111</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1675</v>
+        <v>-0.0207</v>
       </c>
       <c r="V6" t="n">
         <v>1.0895</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4044</v>
+        <v>-1.021</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5551</v>
+        <v>0.8444</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9595</v>
+        <v>-1.8654</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3413</v>
@@ -1000,13 +1000,13 @@
         <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9776</v>
+        <v>0.3611</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0914</v>
+        <v>0.3807</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1137</v>
+        <v>-0.0196</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6342</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9871</v>
+        <v>-1.4469</v>
       </c>
       <c r="E8" t="n">
-        <v>1.555</v>
+        <v>1.0325</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5421</v>
+        <v>-2.4794</v>
       </c>
       <c r="G8" t="n">
         <v>0.7114</v>
@@ -1078,13 +1078,13 @@
         <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.887</v>
+        <v>0.4272</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9705</v>
+        <v>0.448</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0834</v>
+        <v>-0.0207</v>
       </c>
       <c r="V8" t="n">
         <v>-3.2684</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5168</v>
+        <v>-1.4854</v>
       </c>
       <c r="E9" t="n">
         <v>-0.9443</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5725</v>
+        <v>-0.5411</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6061</v>
@@ -1156,13 +1156,13 @@
         <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2764</v>
+        <v>-0.2451</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2091</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0673</v>
+        <v>-0.0359</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0895</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>E. FRIDRIKSSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9854</v>
+        <v>-2.3141</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1495</v>
+        <v>-1.9472</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1641</v>
+        <v>-0.3668</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5348</v>
+        <v>-3.1897</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2418</v>
+        <v>0.8819</v>
       </c>
       <c r="I10" t="n">
-        <v>1.293</v>
+        <v>-4.0715</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5184</v>
+        <v>-1.0399</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3717</v>
+        <v>1.4856</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1467</v>
+        <v>-2.5255</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0164</v>
+        <v>-2.1497</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.13</v>
+        <v>-0.6037</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1463</v>
+        <v>-1.546</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.325</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.6908</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3658</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1952</v>
+        <v>0.1032</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0229</v>
+        <v>-0.0863</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2181</v>
+        <v>0.1895</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. FRIDRIKSSON</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0701</v>
+        <v>-2.7415</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6092</v>
+        <v>-4.031</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4609</v>
+        <v>1.2895</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1897</v>
+        <v>1.5348</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8819</v>
+        <v>0.2418</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.0715</v>
+        <v>1.293</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0399</v>
+        <v>1.5184</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4856</v>
+        <v>0.3717</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5255</v>
+        <v>1.1467</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1497</v>
+        <v>0.0164</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6037</v>
+        <v>-0.13</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.546</v>
+        <v>0.1463</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2276</v>
+        <v>-4.325</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3658</v>
+        <v>-5.6908</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5934</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6528</v>
+        <v>0.0487</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7482</v>
+        <v>0.1414</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0954</v>
+        <v>-0.0926</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3019</v>
+        <v>-4.3576</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4687</v>
+        <v>-0.5871</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8332</v>
+        <v>-3.7704</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8847</v>
@@ -1390,13 +1390,13 @@
         <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5341</v>
+        <v>0.4784</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5805</v>
+        <v>0.4621</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0464</v>
+        <v>0.0163</v>
       </c>
       <c r="V12" t="n">
         <v>-3.2684</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5257</v>
+        <v>-4.4943</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0208</v>
+        <v>-4.2404</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5049</v>
+        <v>-0.254</v>
       </c>
       <c r="G13" t="n">
         <v>-3.5604</v>
@@ -1468,13 +1468,13 @@
         <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0547</v>
+        <v>-0.0234</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7482</v>
+        <v>0.0322</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3065</v>
+        <v>-0.0556</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.701899999999999</v>
+        <v>-6.353399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2903999999999991</v>
+        <v>0.05809999999999871</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.411500000000001</v>
+        <v>-6.4115</v>
       </c>
       <c r="G14" t="n">
         <v>-6.6077</v>
@@ -1537,7 +1537,7 @@
         <v>-6.9984</v>
       </c>
       <c r="P14" t="n">
-        <v>4.552700000000001</v>
+        <v>4.552700000000002</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.3815</v>
@@ -1546,10 +1546,10 @@
         <v>15.9343</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2056</v>
+        <v>2.554</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1115</v>
+        <v>1.4601</v>
       </c>
       <c r="U14" t="n">
         <v>1.0943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9537</v>
+        <v>6.3486</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0769</v>
+        <v>5.1293</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8768</v>
+        <v>1.2193</v>
       </c>
       <c r="G15" t="n">
         <v>4.2601</v>
@@ -1624,13 +1624,13 @@
         <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6529</v>
+        <v>1.0477</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6022</v>
+        <v>0.6546</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0507</v>
+        <v>0.3931</v>
       </c>
       <c r="V15" t="n">
         <v>2.1789</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1254</v>
+        <v>2.6387</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5819</v>
+        <v>1.9372</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5436</v>
+        <v>0.7015</v>
       </c>
       <c r="G16" t="n">
         <v>3.9138</v>
@@ -1702,13 +1702,13 @@
         <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6502</v>
+        <v>-0.137</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6273</v>
+        <v>-0.272</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0229</v>
+        <v>0.135</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4739</v>
+        <v>1.9628</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0562</v>
+        <v>0.1807</v>
       </c>
       <c r="F17" t="n">
-        <v>1.53</v>
+        <v>1.782</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7398</v>
@@ -1780,13 +1780,13 @@
         <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1834</v>
+        <v>0.3055</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1862</v>
+        <v>0.0507</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0028</v>
+        <v>0.2548</v>
       </c>
       <c r="V17" t="n">
         <v>5.2182</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0277</v>
+        <v>1.4225</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1237</v>
+        <v>3.3605</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.096</v>
+        <v>-1.9381</v>
       </c>
       <c r="G18" t="n">
         <v>1.1727</v>
@@ -1858,13 +1858,13 @@
         <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7385</v>
+        <v>-0.3436</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5576</v>
+        <v>-0.3207</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1808</v>
+        <v>-0.0229</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5447</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.952</v>
+        <v>0.8838</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6675</v>
+        <v>-0.1546</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2845</v>
+        <v>1.0385</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1042</v>
+        <v>0.3415</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4766</v>
+        <v>-0.1696</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3724</v>
+        <v>0.511</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0172</v>
+        <v>0.0545</v>
       </c>
       <c r="K19" t="n">
         <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.287</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4593</v>
+        <v>-0.1868</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3724</v>
+        <v>0.4738</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2276</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2276</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6202</v>
+        <v>0.0871</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6502</v>
+        <v>-0.2091</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0301</v>
+        <v>0.2962</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9152</v>
+        <v>0.5026</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1546</v>
+        <v>0.3121</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0698</v>
+        <v>0.1904</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3415</v>
+        <v>0.1042</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1696</v>
+        <v>0.4766</v>
       </c>
       <c r="I20" t="n">
-        <v>0.511</v>
+        <v>-0.3724</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0545</v>
+        <v>0.0172</v>
       </c>
       <c r="K20" t="n">
         <v>0.0172</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0372</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.287</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1868</v>
+        <v>0.4593</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4738</v>
+        <v>-0.3724</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4553</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4553</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1185</v>
+        <v>0.1707</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2091</v>
+        <v>0.2949</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3276</v>
+        <v>-0.1242</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1453</v>
+        <v>-0.0722</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5714</v>
+        <v>-0.2161</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4262</v>
+        <v>0.1439</v>
       </c>
       <c r="G21" t="n">
         <v>0.4526</v>
@@ -2092,13 +2092,13 @@
         <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0532</v>
+        <v>0.0199</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6273</v>
+        <v>-0.272</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.2919</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5447</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3679</v>
+        <v>-0.142</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7919</v>
+        <v>-0.0238</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1598</v>
+        <v>-0.1183</v>
       </c>
       <c r="G22" t="n">
-        <v>1.142</v>
+        <v>-0.1235</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2178</v>
+        <v>-0.8041</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.07580000000000001</v>
+        <v>0.6806</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1404</v>
+        <v>0.002</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1032</v>
+        <v>-0.6452</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0372</v>
+        <v>0.6473</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0016</v>
+        <v>-0.1255</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1146</v>
+        <v>-0.1588</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.113</v>
+        <v>0.0333</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4553</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4553</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8757</v>
+        <v>-0.2462</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3485</v>
+        <v>0.0229</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5272</v>
+        <v>-0.2691</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0895</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
         <v>-1.0895</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8018</v>
+        <v>-0.2111</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0238</v>
+        <v>0.7919</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7781</v>
+        <v>-1.003</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1235</v>
+        <v>1.142</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8041</v>
+        <v>1.2178</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6806</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.002</v>
+        <v>1.1404</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6452</v>
+        <v>1.1032</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6473</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1255</v>
+        <v>0.0016</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1588</v>
+        <v>0.1146</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0333</v>
+        <v>-0.113</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2276</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3658</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9059</v>
+        <v>-0.7188</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0229</v>
+        <v>-0.3485</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.3703</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-1.0895</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5498</v>
+        <v>-1.1653</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1709</v>
+        <v>-1.0481</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3789</v>
+        <v>-0.1172</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7404</v>
+        <v>-1.9438</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5762</v>
+        <v>-0.7239</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8359</v>
+        <v>-1.2198</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8223</v>
+        <v>-1.2026</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4554</v>
+        <v>-0.8521</v>
       </c>
       <c r="L24" t="n">
-        <v>0.633</v>
+        <v>-0.3505</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.918</v>
+        <v>-0.7412</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1209</v>
+        <v>0.1281</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2028</v>
+        <v>-0.8694</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9105</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9105</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7199</v>
+        <v>-0.8071</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3485</v>
+        <v>-0.2929</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3714</v>
+        <v>-0.5141</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0469</v>
+        <v>-1.5498</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5219</v>
+        <v>-1.1709</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.525</v>
+        <v>-0.3789</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9438</v>
+        <v>-1.7404</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7239</v>
+        <v>-2.5762</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2198</v>
+        <v>0.8359</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2026</v>
+        <v>-0.8223</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8521</v>
+        <v>-1.4554</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3505</v>
+        <v>0.633</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7412</v>
+        <v>-0.918</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1281</v>
+        <v>-1.1209</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8694</v>
+        <v>0.2028</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1382</v>
+        <v>0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1382</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6886</v>
+        <v>-0.7199</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7667</v>
+        <v>-0.3485</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.3714</v>
       </c>
       <c r="V25" t="n">
-        <v>2.7237</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.7237</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.8345</v>
+        <v>-3.1271</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3316</v>
+        <v>-2.687</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5029</v>
+        <v>-0.4402</v>
       </c>
       <c r="G26" t="n">
         <v>0.7683</v>
@@ -2482,13 +2482,13 @@
         <v>0.6829</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2183</v>
+        <v>-0.0743</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3017</v>
+        <v>-0.0536</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0834</v>
+        <v>-0.0207</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0895</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>6.701700000000001</v>
+        <v>7.491500000000002</v>
       </c>
       <c r="E27" t="n">
-        <v>6.4115</v>
+        <v>6.411200000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2901999999999998</v>
+        <v>1.079900000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>6.607699999999999</v>
+        <v>6.6077</v>
       </c>
       <c r="H27" t="n">
         <v>0.5730999999999994</v>
@@ -2536,7 +2536,7 @@
         <v>10.6668</v>
       </c>
       <c r="K27" t="n">
-        <v>3.668499999999999</v>
+        <v>3.6685</v>
       </c>
       <c r="L27" t="n">
         <v>6.9981</v>
@@ -2545,10 +2545,10 @@
         <v>-4.059200000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>-3.0955</v>
+        <v>-3.095499999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.9639000000000001</v>
+        <v>-0.9638999999999999</v>
       </c>
       <c r="P27" t="n">
         <v>-4.5528</v>
@@ -2560,13 +2560,13 @@
         <v>11.3818</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.2055</v>
+        <v>-1.416</v>
       </c>
       <c r="T27" t="n">
         <v>-1.0942</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.1114</v>
+        <v>-0.3217</v>
       </c>
       <c r="V27" t="n">
         <v>6.852400000000001</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104759_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104759_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-12.773</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104759_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-5.9208</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
